--- a/pdf2img/hasil_ekstraksi/table_12/tabel_1.xlsx
+++ b/pdf2img/hasil_ekstraksi/table_12/tabel_1.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,1068 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>LAPORAN POSISI KEUANGAN Per 31 Desember 2025 dan 31 Desember 2024d</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>LAPORAN POSISI KEUANGAN Per 31 Desember 2025 dan 31 Desember 2024d.1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LAPORAN POSISI KEUANGAN Per 31 Desember 2025 dan 31 Desember 2024d.2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LAPORAN POSISI KEUANGAN Per 31 Desember 2025 dan 31 Desember 2024d.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>POS : POS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>31.O0s.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>No. "ASET</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>31s2$</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Kart</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>343377</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>374 $23</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pener-patar padia (arn Indoreta</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>19427</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>'4 711 234</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Pener-patar pada bart lain</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>231349</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1 413 94.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tagihan yoot dan tervafl orwardd</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Surat berharga yang dimdiy</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1 816 223</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8199 4*)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Surs berhaga yang dal dengar anji dibel teball repo)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>400 300</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Taghan afat tural berarga yarg dibed dengar jan dija tabal reverte</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>44 979 rego</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Tagihan acsegrat</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>53648</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>16.3 8.2.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>od yang diberk.ar"</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>08151732</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>106 532 499</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pembayaa tyarar</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Peryertaar modal</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>86728</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4868 748</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>'2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Atef Le,argan lainrya Cadangar terugian peryrunan da atet keuargan .</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>')</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sua beraga yang di</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>(64</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ke yar'g diberhar dan perbayaan tyarath</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>19.313 0.2 343</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1' 398 210</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>airya Ater. an ermju</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Atyrnuhas amorltats atet ndan berwu ud wi.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>'S</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Aset botap dan ivertart</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>4283 132</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>$ 383 732</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Asyha eyu, a atet eta an er ta</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>12903</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1 $.3 00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Aset nor produag</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>oger erengala</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>070 503</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Agunan yarg dharbi aui.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>23'768</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>290 0' y</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Rekoring Lurda</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Atet arartance</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>.?</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Atet. lairry</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>13 614 3$0</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0332 374</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TOTAL ASET</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>163 82$ 380</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1$0 184 179</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Liao stas Dan Ekurias</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Liabeias</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Giro</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>$ 841 198</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>4919 36</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Tabunga"</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>10 973 734</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>'0 137 596</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Dego</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2.2 2</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1*1 293 823</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Uang cent*onik</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abll tat teads Bar Indcretia</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Jabll tns cepada bar ain</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2 970 517</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1 80' 068</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>abdl tas spct dar Cerra fonward</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>'3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>abl as afat turat berarga yang dijal Sengan ar ed tenbai (regy</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>394 24</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>bdi tas atsegtarto</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>$3648</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>16.3 8.2.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Surat berarga yang dterd.ar</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>OIC CCO</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>801 6.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Pirpar ar pemsyaar yang dherma</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>4445</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>80 00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>'?</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Setoran aaran</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>4 133</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>naiball tas arfarkarnor abdl tat arrys</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>4353263</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>4 's</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Keper rgar minorat mnorfy rdere</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2 821 283</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>TotAL LiaBajTAs</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>146 760 261</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>133 244 905</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Ikurias</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Wodal rtscticr</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Wodal atar</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>$ 30C C00</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>5 300 0C</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Wodal yarg belu dirnetor</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>391 44 *</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>131461</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Sahan yang dibel eral eatury sot Iambaa nodal etor</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>8 34 829</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>8 344 829</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Agio</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>4 Dagho</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Dana setor ar moda</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2 '44 516</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>214456</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>4 ainny$</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>errgl lain</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Keuarrtungar</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>15.38 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Kerug.ar</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Catangar</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>131 60IC</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Cadanga mm</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Cadiangar Luquan</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20 abaug</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Tghynta*,r lany</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>J457 984</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>3 396 00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Tahun bergarian</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>29.973</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>23 313</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>TOTAL EKurTAs</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Dviden yarg dibayar'car</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>17 06$ 119 163.82$.300</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>16 939 270 150.184 17$</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>-Total LiaBasias Dan Ekuitas</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/pdf2img/hasil_ekstraksi/table_12/tabel_1.xlsx
+++ b/pdf2img/hasil_ekstraksi/table_12/tabel_1.xlsx
@@ -452,12 +452,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C76"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -473,109 +474,154 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>Unnamed: 2</t>
+          <t>31-Des-25</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>31-Des-24</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>ASET Kas 1.</t>
-        </is>
-      </c>
+      <c r="A2" s="3" t="inlineStr"/>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>31-Des-25</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>365.577 19.361.427 2.311.049</t>
+          <t>ASET</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr"/>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>374.523</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2. Penempatan pada Bank Indonesia</t>
+          <t>1. Kas 2.</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>31-Des-24 374.523 14.711.234 1.410.942</t>
+          <t>365.577</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>14.711.234</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>3. Penempatan pada bank lain</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr"/>
-      <c r="C4" s="3" t="inlineStr"/>
+      <c r="A4" s="3" t="inlineStr"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Penempatan pada Bank Indonesia</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>19.361.427</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>4. Tagihan spot dan derivatif/forward</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Penempatan pada bank lain</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>2.311.049</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>1.410.942</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>5. Surat berharga yang dimiliki</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr"/>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>7.874.225 8.199.413</t>
-        </is>
-      </c>
+          <t>4.</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Tagihan spot dan derivatf/forward</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6.</t>
+          <t>5.</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Surat berharga yang dijual dengan janji dibeli kembali (repo)</t>
+          <t>Surat berharga yang dimiliki</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>400.000 163.822 106.532.459</t>
+          <t>7.874.225</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>8.199.413</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t>6.</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Surat berharga yang dijual dengan janji dibeli kembali (repo)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>400.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
           <t>7.</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Tagihan atas surat berharga yang dibeli dengan janji dijual kembali (reverse repo)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr"/>
-      <c r="B9" s="3" t="inlineStr"/>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>144.979 53.648</t>
-        </is>
-      </c>
+          <t>144.979</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -590,7 +636,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>108.151.752</t>
+          <t>53.648</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>163.822</t>
         </is>
       </c>
     </row>
@@ -602,62 +653,67 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Kredit yang diberikan Pembiayaan syariah</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr"/>
+          <t>Kredit yang diberikan</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>108.151.752</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>106.532.459</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>10. 1</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr"/>
+      <c r="A12" s="3" t="inlineStr"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>10.Pembiayaan syariah</t>
+        </is>
+      </c>
       <c r="C12" s="3" t="inlineStr"/>
+      <c r="D12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>11. Penyertaan modal</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr"/>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>12. Aset keuangan lainnya</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>8.966.728</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>12.</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Aset keuangan lainnya</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>4.868.748</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>13.</t>
-        </is>
-      </c>
+      <c r="A15" s="3" t="inlineStr"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Cadangan kerugian penurunan nilai aset keuangan -/-</t>
+          <t>13. Cadangan kerugian penurunan nilai aset keuangan -/-</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr"/>
@@ -671,6 +727,7 @@
           <t>(64)</t>
         </is>
       </c>
+      <c r="D16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr"/>
@@ -681,7 +738,12 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>(1.315.082) (1.398.210)</t>
+          <t>(1.315.082)</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>(1.398.210)</t>
         </is>
       </c>
     </row>
@@ -694,18 +756,24 @@
       <c r="B18" s="3" t="inlineStr"/>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>(340) (690)</t>
+          <t>(340)</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>(690)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>14. Aset tidak berwujud</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr"/>
+      <c r="A19" s="3" t="inlineStr"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>14.Aset tidak berwujud</t>
+        </is>
+      </c>
       <c r="C19" s="3" t="inlineStr"/>
+      <c r="D19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr"/>
@@ -715,17 +783,23 @@
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr"/>
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>15. Aset tetap dan inventaris</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr"/>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>4.285.132 5.383.732</t>
+          <t>4.285.132</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>5.383.732</t>
         </is>
       </c>
     </row>
@@ -733,23 +807,29 @@
       <c r="A22" s="3" t="inlineStr"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Akumulasi penyusutan aset tetap dan inventaris --</t>
+          <t>Akumulasi penyusutan aset tetap dan inventaris -/-</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>(1.290.371) (1.153.085)</t>
+          <t>(1.290.371)</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>(1.153.085)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>16.Aset non produktif</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr"/>
+      <c r="A23" s="3" t="inlineStr"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>16. Aset non produktif</t>
+        </is>
+      </c>
       <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr"/>
@@ -763,6 +843,7 @@
           <t>1.070.593</t>
         </is>
       </c>
+      <c r="D24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr"/>
@@ -773,18 +854,24 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>231.768 298.913</t>
+          <t>231.768</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>298.913</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr"/>
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>c. Rekening tunda</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr"/>
       <c r="C26" s="3" t="inlineStr"/>
+      <c r="D26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr"/>
@@ -794,112 +881,145 @@
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr"/>
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>17.Aset lainnya</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr"/>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>13.614.359 10.392.374</t>
+          <t>13.614.359</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>10.392.374 150.184.175</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr"/>
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>TOTAL ASET</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr"/>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>163.825.380 150.184.175</t>
-        </is>
-      </c>
+          <t>163.825.380</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>LIABILITAS DAN EKUITAS</t>
+          <t>LIABILITAS DAN EKUITAS LIABILITAS</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr"/>
+      <c r="D30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>LIABILITAS</t>
+          <t>1. Giro</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr"/>
       <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>4.919.367</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>1. Giro</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr"/>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>.Tabungan</t>
+        </is>
+      </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>5.841.198 4.919.367 10.157.596</t>
+          <t>5.841.198 10.972.734</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>10.157.596</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2. Tabungan</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr"/>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Deposito</t>
+        </is>
+      </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>10.972.734 111.295.823</t>
+          <t>121.962.256</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>111.295.823</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3. Deposito</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr"/>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>121.962.256</t>
-        </is>
-      </c>
+          <t>4.</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Uang elektronik</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr"/>
+      <c r="D34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>4.</t>
+          <t>5.</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Uang elektronik</t>
+          <t>Liabilitas kepada Bank Indonesia</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>5.</t>
+          <t>6.</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Liabiitas kepada Bank Indonesia</t>
+          <t>Liabilitas kepada bank lain</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -907,21 +1027,23 @@
           <t>2.970.517</t>
         </is>
       </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>1.801.048</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>6.</t>
-        </is>
-      </c>
+      <c r="A37" s="3" t="inlineStr"/>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Liabilitas kepada bank lain</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>1.801.048</t>
+          <t>Liabilitas spot dan derivatif/ forward</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -933,416 +1055,439 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Liabilitas spot dan derivatif/forward</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>-Liabilitas atas surat berharga yang dijual dengan janji dibeli kembali (repo)</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr"/>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>394.214</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>8.</t>
+          <t>8. 9.</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Liabilitas atas surat berharga yang dijual dengan janji dibeli kembali (repo).</t>
+          <t>.Liabilitas akseptasi</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>394.214</t>
+          <t>53.648</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>163.822</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>9. Liabiitas akseptasi</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr"/>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>53.648 163.822</t>
+      <c r="A40" s="3" t="inlineStr"/>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>10.Surat berharga yang diterbitkan</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr"/>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>801.632</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>10.</t>
-        </is>
-      </c>
+      <c r="A41" s="3" t="inlineStr"/>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Surat berharga yang diterbitkan</t>
+          <t>11. Pinjaman/pembiayaan yang diterima</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>801.632</t>
+          <t>600.000</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>880.000</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>11. 1</t>
-        </is>
-      </c>
+      <c r="A42" s="3" t="inlineStr"/>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Pinjaman/pembiayaan yang diterima</t>
+          <t>12. Setoran jaminan</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>600.000 880.000</t>
+          <t>4.645</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>4.103</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>12. Setoran jaminan</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr"/>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>4.645 4.103</t>
-        </is>
-      </c>
+      <c r="A43" s="3" t="inlineStr"/>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>13.Liabilitas antarkantor</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>13. Liabilitas antarkantor</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr"/>
-      <c r="C44" s="3" t="inlineStr"/>
+      <c r="A44" s="3" t="inlineStr"/>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>14.Liabilitas lainnya</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>4.355.263</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>2.827.285</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>14. Liabilitas annya</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr"/>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>4.355.263 2.827.285</t>
-        </is>
-      </c>
+      <c r="A45" s="3" t="inlineStr"/>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>15. Kepentingan minoritas (minority interest)</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>15. Kepentingan minoritas (minority interest)</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr"/>
-      <c r="C46" s="3" t="inlineStr"/>
+      <c r="A46" s="3" t="inlineStr"/>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL LiABILITAS</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>146.760.261</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>133.244.905</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>TOTAL LiABILITAS</t>
+          <t>EKUITAS</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr"/>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>146.760.261 133.244.905</t>
-        </is>
-      </c>
+      <c r="C47" s="3" t="inlineStr"/>
+      <c r="D47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>EKUITAS</t>
+          <t>16.Modal disetor</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr"/>
       <c r="C48" s="3" t="inlineStr"/>
+      <c r="D48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>16.Modal disetor</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr"/>
-      <c r="C49" s="3" t="inlineStr"/>
+      <c r="A49" s="3" t="inlineStr"/>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>a. Modal dasar</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>5.300.000</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>5.300.000</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>a. Modal dasar</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr"/>
+      <c r="A50" s="3" t="inlineStr"/>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>b. Modal yang belum disetor -/-</t>
+        </is>
+      </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>5.300.000 5.300.000</t>
+          <t>(3.961.461)</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>(3.961.461)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>b. Modal yang belum disetor -/-</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr"/>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>(3.961.461) (3.961.461)</t>
-        </is>
-      </c>
+      <c r="A51" s="3" t="inlineStr"/>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>c. Saham yang dibeli kembali (treasury stock) -/-</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr"/>
+      <c r="D51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>c. Saham yang dibeli kembali (reasury stock) --</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr"/>
+      <c r="A52" s="3" t="inlineStr"/>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>17.Tambahan modal disetor</t>
+        </is>
+      </c>
       <c r="C52" s="3" t="inlineStr"/>
+      <c r="D52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>17.Tambahan modal disetor</t>
+          <t>a. Agio</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr"/>
-      <c r="C53" s="3" t="inlineStr"/>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>8.364.829</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>8.364.829</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>a. Agio</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr"/>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>8.364.829 8.364.829</t>
-        </is>
-      </c>
+      <c r="A54" s="3" t="inlineStr"/>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>b. Disagio --</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr"/>
+      <c r="D54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>b. Disagio -/-</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr"/>
+      <c r="A55" s="3" t="inlineStr"/>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>c. Dana setoran modal</t>
+        </is>
+      </c>
       <c r="C55" s="3" t="inlineStr"/>
+      <c r="D55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>c. Dana setoran modal</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr"/>
+      <c r="A56" s="3" t="inlineStr"/>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>d. Lainnya</t>
+        </is>
+      </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
           <t>2.144.516</t>
         </is>
       </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>2.144.516</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>d. Lainnya</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr"/>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>2.144.516</t>
-        </is>
-      </c>
+      <c r="A57" s="3" t="inlineStr"/>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>18.Penghasilan komprehensif lain</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr"/>
+      <c r="D57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>18.Penghasilan komprehensif lain</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr"/>
+      <c r="A58" s="3" t="inlineStr"/>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>a. Keuntungan</t>
+        </is>
+      </c>
       <c r="C58" s="3" t="inlineStr"/>
+      <c r="D58" s="3" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>a. Keuntungan</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr"/>
-      <c r="C59" s="3" t="inlineStr"/>
+      <c r="A59" s="3" t="inlineStr"/>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>b. Kerugian --</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>1.596.676</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>1.538.212</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>b. Kerugian --</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr"/>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>1.596.676 1.538.212</t>
-        </is>
-      </c>
+      <c r="A60" s="3" t="inlineStr"/>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>19.Cadangan</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr"/>
+      <c r="D60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>19.Cadangan</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr"/>
-      <c r="C61" s="3" t="inlineStr"/>
+      <c r="A61" s="3" t="inlineStr"/>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>a. Cadangan umum</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>132.600</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>131.600</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>a. Cadangan umum</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr"/>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>131.600</t>
-        </is>
-      </c>
+      <c r="A62" s="3" t="inlineStr"/>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>b. Cadangan tujuan</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr"/>
+      <c r="D62" s="3" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>b. Cadangan tujuan</t>
-        </is>
-      </c>
+      <c r="A63" s="3" t="inlineStr"/>
       <c r="B63" s="3" t="inlineStr"/>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>132.600</t>
-        </is>
-      </c>
+      <c r="C63" s="3" t="inlineStr"/>
+      <c r="D63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr"/>
-      <c r="B64" s="3" t="inlineStr"/>
-      <c r="C64" s="3" t="inlineStr"/>
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>20.Laba/rugi</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Ja. Tahun-tahun lalu</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>3.457.984</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>20. Laba/rugi</t>
-        </is>
-      </c>
+      <c r="A65" s="3" t="inlineStr"/>
       <c r="B65" s="3" t="inlineStr"/>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>3.457.984</t>
+      <c r="C65" s="3" t="inlineStr"/>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>3.396.001</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>a. Tahun-tahun lalu</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr"/>
+      <c r="A66" s="3" t="inlineStr"/>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>b. Tahun berjalan</t>
+        </is>
+      </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>3.396.001</t>
+          <t>29.975</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>25.573</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>b. Tahun berjalan</t>
-        </is>
-      </c>
+      <c r="A67" s="3" t="inlineStr"/>
       <c r="B67" s="3" t="inlineStr"/>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>29.975</t>
-        </is>
-      </c>
+      <c r="C67" s="3" t="inlineStr"/>
+      <c r="D67" s="3" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr"/>
-      <c r="B68" s="3" t="inlineStr"/>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>25.573</t>
-        </is>
-      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>c. Dividen yang dibayarkan -/-</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr"/>
+      <c r="D68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr"/>
       <c r="B69" s="3" t="inlineStr"/>
       <c r="C69" s="3" t="inlineStr"/>
+      <c r="D69" s="3" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr"/>
-      <c r="B70" s="3" t="inlineStr"/>
-      <c r="C70" s="3" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>c. Dividen yang dibayarkan -/-</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr"/>
-      <c r="C71" s="3" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr"/>
-      <c r="B72" s="3" t="inlineStr"/>
-      <c r="C72" s="3" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr"/>
-      <c r="B73" s="3" t="inlineStr"/>
-      <c r="C73" s="3" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr"/>
-      <c r="B74" s="3" t="inlineStr"/>
-      <c r="C74" s="3" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr"/>
-      <c r="B75" s="3" t="inlineStr"/>
-      <c r="C75" s="3" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>TOTAL EKUITAS TOTAL LIABILITAS DAN EKUITAS</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>17.065.119 163.825.380</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>16.939.270 150.184.175</t>
         </is>
@@ -1359,758 +1504,822 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C69"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>1. Kas 2.</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>POS - POS</t>
+          <t>Penempatan pada Bank Indonesia</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>Unnamed: 2</t>
+          <t>365.577 19.361.427</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>14.711.234</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>ASET Kas 1.</t>
-        </is>
+      <c r="A2" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>31-Des-25</t>
+          <t>Penempatan pada bank lain</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3.655771936142723e+20</v>
+        <v>2311049</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>1410942</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>2. Penempatan pada Bank Indonesia</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>31-Des-24 374.523 14.711.234 1.410.942</t>
-        </is>
-      </c>
+      <c r="A3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Tagihan spot dan derivatf/forward</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>3. Penempatan pada bank lain</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr"/>
-      <c r="C4" s="3" t="inlineStr"/>
+      <c r="A4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Surat berharga yang dimiliki</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>7874225</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>8199413</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>4. Tagihan spot dan derivatif/forward</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr"/>
+      <c r="A5" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Surat berharga yang dijual dengan janji dibeli kembali (repo)</t>
+        </is>
+      </c>
       <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>5. Surat berharga yang dimiliki</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr"/>
+      <c r="A6" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Tagihan atas surat berharga yang dibeli dengan janji dijual kembali (reverse repo)</t>
+        </is>
+      </c>
       <c r="C6" s="3" t="n">
-        <v>78742258199413</v>
-      </c>
+        <v>144.979</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Surat berharga yang dijual dengan janji dibeli kembali (repo)</t>
+          <t>Tagihan akseptasi</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>4.000001638221065e+20</v>
+        <v>53.648</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>163.822</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Tagihan atas surat berharga yang dibeli dengan janji dijual kembali (reverse repo)</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr"/>
+          <t>Kredit yang diberikan</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>108151752</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>106532459</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr"/>
-      <c r="B9" s="3" t="inlineStr"/>
-      <c r="C9" s="3" t="n">
-        <v>14497953648</v>
-      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>10.Pembiayaan syariah</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="A10" s="3" t="inlineStr"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Tagihan akseptasi</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>108151752</v>
-      </c>
+          <t>11. Penyertaan modal</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr"/>
+      <c r="D10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>9</v>
-      </c>
+      <c r="A11" s="3" t="inlineStr"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Kredit yang diberikan Pembiayaan syariah</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr"/>
+          <t>12. Aset keuangan lainnya</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>8966728</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>4868748</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr"/>
+      <c r="A12" s="3" t="inlineStr"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>13. Cadangan kerugian penurunan nilai aset keuangan -/-</t>
+        </is>
+      </c>
       <c r="C12" s="3" t="inlineStr"/>
+      <c r="D12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>11. Penyertaan modal</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr"/>
+      <c r="A13" s="3" t="inlineStr"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>a. Surat berharga yang dimiliki</t>
+        </is>
+      </c>
       <c r="C13" s="3" t="n">
-        <v>8966728</v>
-      </c>
+        <v>-64</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>12</v>
-      </c>
+      <c r="A14" s="3" t="inlineStr"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Aset keuangan lainnya</t>
+          <t>b. Kredit yang diberikan dan pembiayaan syariah</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>4868748</v>
+        <v>-1315082</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>-1398210</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Cadangan kerugian penurunan nilai aset keuangan -/-</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr"/>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>c. Lainnya</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="n">
+        <v>-340</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>-690</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr"/>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>a. Surat berharga yang dimiliki</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>-64</v>
-      </c>
+          <t>14.Aset tidak berwujud</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr"/>
+      <c r="D16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>b. Kredit yang diberikan dan pembiayaan syariah</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>(1.315.082) (1.398.210)</t>
-        </is>
-      </c>
+          <t>Akumulasi amortisasi aset tidak berwujud -/-</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>c. Lainnya</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr"/>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>(340) (690)</t>
-        </is>
+      <c r="A18" s="3" t="inlineStr"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>15. Aset tetap dan inventaris</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>4285132</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>5383732</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>14. Aset tidak berwujud</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr"/>
-      <c r="C19" s="3" t="inlineStr"/>
+      <c r="A19" s="3" t="inlineStr"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Akumulasi penyusutan aset tetap dan inventaris -/-</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>-1290371</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>-1153085</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Akumulasi amortisasi aset tidak berwujud -/-</t>
+          <t>16. Aset non produktif</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>15. Aset tetap dan inventaris</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr"/>
+      <c r="A21" s="3" t="inlineStr"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>a. Properti terbengkalai</t>
+        </is>
+      </c>
       <c r="C21" s="3" t="n">
-        <v>42851325383732</v>
-      </c>
+        <v>1070593</v>
+      </c>
+      <c r="D21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Akumulasi penyusutan aset tetap dan inventaris --</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>(1.290.371) (1.153.085)</t>
-        </is>
+          <t>b. Agunan yang diambil alih</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>231.768</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>298.913</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>16.Aset non produktif</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr"/>
+      <c r="A23" s="3" t="inlineStr"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>c. Rekening tunda</t>
+        </is>
+      </c>
       <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>a. Properti terbengkalai</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>1070593</v>
-      </c>
+          <t>d. Aset antarkantor</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr"/>
+      <c r="D24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>b. Agunan yang diambil alih</t>
+          <t>17.Aset lainnya</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>231768298913</v>
+        <v>13614359</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>1.039237415018418e+16</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>c. Rekening tunda</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr"/>
-      <c r="C26" s="3" t="inlineStr"/>
+      <c r="A26" s="3" t="inlineStr"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL ASET</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>163825380</v>
+      </c>
+      <c r="D26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>d. Aset antarkantor</t>
+          <t>LIABILITAS DAN EKUITAS LIABILITAS</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>17.Aset lainnya</t>
+          <t>1. Giro</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr"/>
-      <c r="C28" s="3" t="n">
-        <v>1361435910392374</v>
+      <c r="C28" s="3" t="inlineStr"/>
+      <c r="D28" s="3" t="n">
+        <v>4919367</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>TOTAL ASET</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr"/>
+      <c r="A29" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>.Tabungan</t>
+        </is>
+      </c>
       <c r="C29" s="3" t="n">
-        <v>1.638253801501842e+17</v>
+        <v>584119810972734</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>10157596</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr"/>
+      <c r="A30" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>LIABILITAS DAN EKUITAS</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr"/>
+          <t>Deposito</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>121962256</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>111295823</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>LIABILITAS</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr"/>
+      <c r="A31" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Uang elektronik</t>
+        </is>
+      </c>
       <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>1. Giro</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr"/>
-      <c r="C32" s="3" t="n">
-        <v>5.84119849193671e+21</v>
-      </c>
+      <c r="A32" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Liabilitas kepada Bank Indonesia</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr"/>
+      <c r="D32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>2. Tabungan</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr"/>
+      <c r="A33" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Liabilitas kepada bank lain</t>
+        </is>
+      </c>
       <c r="C33" s="3" t="n">
-        <v>1.097273411129582e+16</v>
+        <v>2970517</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>1801048</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>3. Deposito</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr"/>
-      <c r="C34" s="3" t="n">
-        <v>121962256</v>
+      <c r="A34" s="3" t="inlineStr"/>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Liabilitas spot dan derivatif/ forward</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr"/>
+      <c r="D34" s="3" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Uang elektronik</t>
+          <t>-Liabilitas atas surat berharga yang dijual dengan janji dibeli kembali (repo)</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr"/>
+      <c r="D35" s="3" t="n">
+        <v>394.214</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>5</v>
+        <v>89</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Liabiitas kepada Bank Indonesia</t>
+          <t>.Liabilitas akseptasi</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>2970517</v>
+        <v>53.648</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>163.822</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
-        <v>6</v>
-      </c>
+      <c r="A37" s="3" t="inlineStr"/>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Liabilitas kepada bank lain</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>1801048</v>
+          <t>10.Surat berharga yang diterbitkan</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr"/>
+      <c r="D37" s="3" t="n">
+        <v>801.6319999999999</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
-        <v>7</v>
-      </c>
+      <c r="A38" s="3" t="inlineStr"/>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Liabilitas spot dan derivatif/forward</t>
+          <t>11. Pinjaman/pembiayaan yang diterima</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>15</v>
+        <v>600</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>880</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="A39" s="3" t="inlineStr"/>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Liabilitas atas surat berharga yang dijual dengan janji dibeli kembali (repo).</t>
+          <t>12. Setoran jaminan</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>394.214</v>
+        <v>4.645</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>4.103</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>9. Liabiitas akseptasi</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr"/>
-      <c r="C40" s="3" t="n">
-        <v>53648163822</v>
-      </c>
+      <c r="A40" s="3" t="inlineStr"/>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>13.Liabilitas antarkantor</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr"/>
+      <c r="D40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
-        <v>10</v>
-      </c>
+      <c r="A41" s="3" t="inlineStr"/>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Surat berharga yang diterbitkan</t>
+          <t>14.Liabilitas lainnya</t>
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>801.6319999999999</v>
+        <v>4355263</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>2827285</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="A42" s="3" t="inlineStr"/>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Pinjaman/pembiayaan yang diterima</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>600000880000</v>
-      </c>
+          <t>15. Kepentingan minoritas (minority interest)</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr"/>
+      <c r="D42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>12. Setoran jaminan</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr"/>
+      <c r="A43" s="3" t="inlineStr"/>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL LiABILITAS</t>
+        </is>
+      </c>
       <c r="C43" s="3" t="n">
-        <v>46454103</v>
+        <v>146760261</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>133244905</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>13. Liabilitas antarkantor</t>
+          <t>EKUITAS</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr"/>
       <c r="C44" s="3" t="inlineStr"/>
+      <c r="D44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>14. Liabilitas annya</t>
+          <t>16.Modal disetor</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr"/>
-      <c r="C45" s="3" t="n">
-        <v>43552632827285</v>
-      </c>
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>15. Kepentingan minoritas (minority interest)</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr"/>
-      <c r="C46" s="3" t="inlineStr"/>
+      <c r="A46" s="3" t="inlineStr"/>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>a. Modal dasar</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>5300000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>5300000</v>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>TOTAL LiABILITAS</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr"/>
+      <c r="A47" s="3" t="inlineStr"/>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>b. Modal yang belum disetor -/-</t>
+        </is>
+      </c>
       <c r="C47" s="3" t="n">
-        <v>1.467602611332449e+17</v>
+        <v>-3961461</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>-3961461</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>EKUITAS</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr"/>
+      <c r="A48" s="3" t="inlineStr"/>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>c. Saham yang dibeli kembali (treasury stock) -/-</t>
+        </is>
+      </c>
       <c r="C48" s="3" t="inlineStr"/>
+      <c r="D48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>16.Modal disetor</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr"/>
+      <c r="A49" s="3" t="inlineStr"/>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>17.Tambahan modal disetor</t>
+        </is>
+      </c>
       <c r="C49" s="3" t="inlineStr"/>
+      <c r="D49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>a. Modal dasar</t>
+          <t>a. Agio</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr"/>
       <c r="C50" s="3" t="n">
-        <v>53000005300000</v>
+        <v>8364829</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>8364829</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>b. Modal yang belum disetor -/-</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr"/>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>(3.961.461) (3.961.461)</t>
-        </is>
-      </c>
+      <c r="A51" s="3" t="inlineStr"/>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>b. Disagio --</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr"/>
+      <c r="D51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>c. Saham yang dibeli kembali (reasury stock) --</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr"/>
+      <c r="A52" s="3" t="inlineStr"/>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>c. Dana setoran modal</t>
+        </is>
+      </c>
       <c r="C52" s="3" t="inlineStr"/>
+      <c r="D52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>17.Tambahan modal disetor</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr"/>
-      <c r="C53" s="3" t="inlineStr"/>
+      <c r="A53" s="3" t="inlineStr"/>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>d. Lainnya</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>2144516</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>2144516</v>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>a. Agio</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr"/>
-      <c r="C54" s="3" t="n">
-        <v>83648298364829</v>
-      </c>
+      <c r="A54" s="3" t="inlineStr"/>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>18.Penghasilan komprehensif lain</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr"/>
+      <c r="D54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>b. Disagio -/-</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr"/>
+      <c r="A55" s="3" t="inlineStr"/>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>a. Keuntungan</t>
+        </is>
+      </c>
       <c r="C55" s="3" t="inlineStr"/>
+      <c r="D55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>c. Dana setoran modal</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr"/>
+      <c r="A56" s="3" t="inlineStr"/>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>b. Kerugian --</t>
+        </is>
+      </c>
       <c r="C56" s="3" t="n">
-        <v>2144516</v>
+        <v>1596676</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>1538212</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>d. Lainnya</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr"/>
-      <c r="C57" s="3" t="n">
-        <v>2144516</v>
-      </c>
+      <c r="A57" s="3" t="inlineStr"/>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>19.Cadangan</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr"/>
+      <c r="D57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>18.Penghasilan komprehensif lain</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr"/>
-      <c r="C58" s="3" t="inlineStr"/>
+      <c r="A58" s="3" t="inlineStr"/>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>a. Cadangan umum</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>132.6</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>131.6</v>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>a. Keuntungan</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr"/>
+      <c r="A59" s="3" t="inlineStr"/>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>b. Cadangan tujuan</t>
+        </is>
+      </c>
       <c r="C59" s="3" t="inlineStr"/>
+      <c r="D59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>b. Kerugian --</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr"/>
+          <t>20.Laba/rugi</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Ja. Tahun-tahun lalu</t>
+        </is>
+      </c>
       <c r="C60" s="3" t="n">
-        <v>15966761538212</v>
-      </c>
+        <v>3457984</v>
+      </c>
+      <c r="D60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>19.Cadangan</t>
-        </is>
-      </c>
+      <c r="A61" s="3" t="inlineStr"/>
       <c r="B61" s="3" t="inlineStr"/>
       <c r="C61" s="3" t="inlineStr"/>
+      <c r="D61" s="3" t="n">
+        <v>3396001</v>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>a. Cadangan umum</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr"/>
+      <c r="A62" s="3" t="inlineStr"/>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>b. Tahun berjalan</t>
+        </is>
+      </c>
       <c r="C62" s="3" t="n">
-        <v>131.6</v>
+        <v>29.975</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>25.573</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>b. Cadangan tujuan</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr"/>
-      <c r="C63" s="3" t="n">
-        <v>132.6</v>
-      </c>
+      <c r="A63" s="3" t="inlineStr"/>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>c. Dividen yang dibayarkan -/-</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr"/>
+      <c r="D63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>20. Laba/rugi</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr"/>
+      <c r="A64" s="3" t="inlineStr"/>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL EKUITAS TOTAL LIABILITAS DAN EKUITAS</t>
+        </is>
+      </c>
       <c r="C64" s="3" t="n">
-        <v>3457984</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>a. Tahun-tahun lalu</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="inlineStr"/>
-      <c r="C65" s="3" t="n">
-        <v>3396001</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>b. Tahun berjalan</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr"/>
-      <c r="C66" s="3" t="n">
-        <v>29.975</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr"/>
-      <c r="B67" s="3" t="inlineStr"/>
-      <c r="C67" s="3" t="n">
-        <v>25.573</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>c. Dividen yang dibayarkan -/-</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr"/>
-      <c r="C68" s="3" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>TOTAL EKUITAS TOTAL LIABILITAS DAN EKUITAS</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="n">
         <v>1.706511916382538e+16</v>
       </c>
-      <c r="C69" s="3" t="n">
+      <c r="D64" s="3" t="n">
         <v>1.693927015018418e+16</v>
       </c>
     </row>
